--- a/tams-disclosure-parent/tams-disclosure/src/main/resources/tpl/ProElementAdjInfo.xlsx
+++ b/tams-disclosure-parent/tams-disclosure/src/main/resources/tpl/ProElementAdjInfo.xlsx
@@ -5,7 +5,7 @@
   <workbookPr codeName="ThisWorkbook" defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Administrator\Desktop\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="F:\nyxp\tams-disclosure-parent\tams-disclosure\src\main\resources\tpl\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
@@ -19,11 +19,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="15" uniqueCount="15">
-  <si>
-    <t>数据状态</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="13" uniqueCount="13">
   <si>
     <t>产品登记编码</t>
     <phoneticPr fontId="2" type="noConversion"/>
@@ -33,10 +29,6 @@
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
-    <t>是否有代销机构</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
     <t>此产品要素调整描述文字1</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
@@ -73,11 +65,11 @@
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
-    <t>更新时间</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>更新人</t>
+    <t>调整此产品要素原因</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>对此要素调整(原因)</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
 </sst>
@@ -484,59 +476,52 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:O1"/>
+  <dimension ref="A1:M1"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="17.08984375" style="1" customWidth="1"/>
-    <col min="2" max="2" width="18.453125" style="1" customWidth="1"/>
-    <col min="3" max="4" width="22.26953125" style="1" customWidth="1"/>
+    <col min="1" max="1" width="18.453125" style="1" customWidth="1"/>
+    <col min="2" max="3" width="22.26953125" style="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:15" ht="56" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:13" ht="56" x14ac:dyDescent="0.25">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
       <c r="B1" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="2" t="s">
+      <c r="C1" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="D1" s="4" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="3" t="s">
+      <c r="E1" s="4" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="4" t="s">
+      <c r="F1" s="4" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="4" t="s">
+      <c r="G1" s="4" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="4" t="s">
+      <c r="H1" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="4" t="s">
+      <c r="I1" s="4" t="s">
         <v>7</v>
       </c>
-      <c r="I1" s="4" t="s">
+      <c r="J1" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="K1" s="4" t="s">
         <v>8</v>
       </c>
-      <c r="J1" s="4" t="s">
+      <c r="L1" s="4" t="s">
         <v>9</v>
       </c>
-      <c r="K1" s="4" t="s">
+      <c r="M1" s="4" t="s">
         <v>10</v>
-      </c>
-      <c r="L1" s="4" t="s">
-        <v>11</v>
-      </c>
-      <c r="M1" s="4" t="s">
-        <v>12</v>
-      </c>
-      <c r="N1" s="4" t="s">
-        <v>13</v>
-      </c>
-      <c r="O1" s="4" t="s">
-        <v>14</v>
       </c>
     </row>
   </sheetData>

--- a/tams-disclosure-parent/tams-disclosure/src/main/resources/tpl/ProElementAdjInfo.xlsx
+++ b/tams-disclosure-parent/tams-disclosure/src/main/resources/tpl/ProElementAdjInfo.xlsx
@@ -481,6 +481,8 @@
   <cols>
     <col min="1" max="1" width="18.453125" style="1" customWidth="1"/>
     <col min="2" max="3" width="22.26953125" style="1" customWidth="1"/>
+    <col min="9" max="9" width="10.26953125" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="9" style="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:13" ht="56" x14ac:dyDescent="0.25">

--- a/tams-disclosure-parent/tams-disclosure/src/main/resources/tpl/ProElementAdjInfo.xlsx
+++ b/tams-disclosure-parent/tams-disclosure/src/main/resources/tpl/ProElementAdjInfo.xlsx
@@ -19,7 +19,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="13" uniqueCount="13">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="16" uniqueCount="16">
   <si>
     <t>产品登记编码</t>
     <phoneticPr fontId="2" type="noConversion"/>
@@ -70,6 +70,18 @@
   </si>
   <si>
     <t>对此要素调整(原因)</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>数据状态</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>更新时间</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>更新人</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
 </sst>
@@ -77,7 +89,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <fonts count="3" x14ac:knownFonts="1">
+  <fonts count="4" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -101,8 +113,16 @@
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <sz val="11"/>
+      <color theme="0"/>
+      <name val="宋体"/>
+      <family val="2"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
-  <fills count="3">
+  <fills count="4">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -113,6 +133,12 @@
       <patternFill patternType="solid">
         <fgColor theme="4" tint="0.59999389629810485"/>
         <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.39997558519241921"/>
+        <bgColor indexed="65"/>
       </patternFill>
     </fill>
   </fills>
@@ -151,12 +177,15 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="1">
+  <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -172,8 +201,12 @@
     <xf numFmtId="49" fontId="1" fillId="2" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
   </cellXfs>
-  <cellStyles count="1">
+  <cellStyles count="2">
+    <cellStyle name="60% - 着色 1" xfId="1" builtinId="32"/>
     <cellStyle name="常规" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
@@ -476,7 +509,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:M1"/>
+  <dimension ref="A1:P1"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="18.453125" style="1" customWidth="1"/>
@@ -485,50 +518,59 @@
     <col min="13" max="13" width="9" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13" ht="56" x14ac:dyDescent="0.25">
-      <c r="A1" s="2" t="s">
+    <row r="1" spans="1:16" ht="56" x14ac:dyDescent="0.25">
+      <c r="A1" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="B1" s="2" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="2" t="s">
+      <c r="C1" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="3" t="s">
+      <c r="D1" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="D1" s="4" t="s">
+      <c r="E1" s="4" t="s">
         <v>2</v>
       </c>
-      <c r="E1" s="4" t="s">
+      <c r="F1" s="4" t="s">
         <v>3</v>
       </c>
-      <c r="F1" s="4" t="s">
+      <c r="G1" s="4" t="s">
         <v>4</v>
       </c>
-      <c r="G1" s="4" t="s">
+      <c r="H1" s="4" t="s">
         <v>5</v>
       </c>
-      <c r="H1" s="4" t="s">
+      <c r="I1" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="I1" s="4" t="s">
+      <c r="J1" s="4" t="s">
         <v>7</v>
       </c>
-      <c r="J1" s="4" t="s">
+      <c r="K1" s="4" t="s">
         <v>12</v>
       </c>
-      <c r="K1" s="4" t="s">
+      <c r="L1" s="4" t="s">
         <v>8</v>
       </c>
-      <c r="L1" s="4" t="s">
+      <c r="M1" s="4" t="s">
         <v>9</v>
       </c>
-      <c r="M1" s="4" t="s">
+      <c r="N1" s="4" t="s">
         <v>10</v>
+      </c>
+      <c r="O1" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="P1" s="4" t="s">
+        <v>15</v>
       </c>
     </row>
   </sheetData>
   <phoneticPr fontId="2" type="noConversion"/>
   <pageMargins left="0.69930555555555596" right="0.69930555555555596" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>
--- a/tams-disclosure-parent/tams-disclosure/src/main/resources/tpl/ProElementAdjInfo.xlsx
+++ b/tams-disclosure-parent/tams-disclosure/src/main/resources/tpl/ProElementAdjInfo.xlsx
@@ -5,11 +5,11 @@
   <workbookPr codeName="ThisWorkbook" defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="F:\nyxp\tams-disclosure-parent\tams-disclosure\src\main\resources\tpl\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\Git\NY\tams-disclosure-parent\tams-disclosure\src\main\resources\tpl\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="24180" windowHeight="13070"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="24180" windowHeight="13065"/>
   </bookViews>
   <sheets>
     <sheet name="产品要素调整信息" sheetId="1" r:id="rId1"/>
@@ -29,14 +29,6 @@
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
-    <t>此产品要素调整描述文字1</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>此产品要素调整描述文字2</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
     <t>调整要素</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
@@ -53,26 +45,10 @@
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
-    <t>调整此要素（补充说明文1）</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>调整此要素（补充说明文2）</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
     <t>报告发布日期</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
-    <t>调整此产品要素原因</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>对此要素调整(原因)</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
     <t>数据状态</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
@@ -82,6 +58,30 @@
   </si>
   <si>
     <t>更新人</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>单产品多要素段1</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>单产品多要素段2</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>单产品多要素段3</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>单要素多产品段1</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>单要素多产品段2</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>单要素多产品段3</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
 </sst>
@@ -510,17 +510,18 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:P1"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" x14ac:dyDescent="0.15"/>
   <cols>
-    <col min="1" max="1" width="18.453125" style="1" customWidth="1"/>
-    <col min="2" max="3" width="22.26953125" style="1" customWidth="1"/>
-    <col min="9" max="9" width="10.26953125" style="1" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="18.5" style="1" customWidth="1"/>
+    <col min="2" max="3" width="22.25" style="1" customWidth="1"/>
+    <col min="4" max="4" width="11.25" customWidth="1"/>
+    <col min="9" max="9" width="10.25" style="1" bestFit="1" customWidth="1"/>
     <col min="13" max="13" width="9" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:16" ht="56" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:16" ht="27" x14ac:dyDescent="0.15">
       <c r="A1" s="5" t="s">
-        <v>13</v>
+        <v>7</v>
       </c>
       <c r="B1" s="2" t="s">
         <v>0</v>
@@ -529,43 +530,43 @@
         <v>1</v>
       </c>
       <c r="D1" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="E1" s="4" t="s">
         <v>11</v>
       </c>
-      <c r="E1" s="4" t="s">
+      <c r="F1" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="G1" s="4" t="s">
         <v>2</v>
       </c>
-      <c r="F1" s="4" t="s">
+      <c r="H1" s="4" t="s">
         <v>3</v>
       </c>
-      <c r="G1" s="4" t="s">
+      <c r="I1" s="4" t="s">
         <v>4</v>
       </c>
-      <c r="H1" s="4" t="s">
+      <c r="J1" s="4" t="s">
         <v>5</v>
       </c>
-      <c r="I1" s="4" t="s">
+      <c r="K1" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="L1" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="M1" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="N1" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="J1" s="4" t="s">
-        <v>7</v>
-      </c>
-      <c r="K1" s="4" t="s">
-        <v>12</v>
-      </c>
-      <c r="L1" s="4" t="s">
+      <c r="O1" s="4" t="s">
         <v>8</v>
       </c>
-      <c r="M1" s="4" t="s">
+      <c r="P1" s="4" t="s">
         <v>9</v>
-      </c>
-      <c r="N1" s="4" t="s">
-        <v>10</v>
-      </c>
-      <c r="O1" s="4" t="s">
-        <v>14</v>
-      </c>
-      <c r="P1" s="4" t="s">
-        <v>15</v>
       </c>
     </row>
   </sheetData>

--- a/tams-disclosure-parent/tams-disclosure/src/main/resources/tpl/ProElementAdjInfo.xlsx
+++ b/tams-disclosure-parent/tams-disclosure/src/main/resources/tpl/ProElementAdjInfo.xlsx
@@ -14,12 +14,12 @@
   <sheets>
     <sheet name="产品要素调整信息" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="144525"/>
+  <calcPr calcId="144525" concurrentCalc="0"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="16" uniqueCount="16">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="17" uniqueCount="17">
   <si>
     <t>产品登记编码</t>
     <phoneticPr fontId="2" type="noConversion"/>
@@ -82,6 +82,10 @@
   </si>
   <si>
     <t>单要素多产品段3</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>子产品名称</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
 </sst>
@@ -509,17 +513,17 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:P1"/>
+  <dimension ref="A1:Q1"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" x14ac:dyDescent="0.15"/>
   <cols>
     <col min="1" max="1" width="18.5" style="1" customWidth="1"/>
-    <col min="2" max="3" width="22.25" style="1" customWidth="1"/>
-    <col min="4" max="4" width="11.25" customWidth="1"/>
-    <col min="9" max="9" width="10.25" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="9" style="1"/>
+    <col min="2" max="4" width="22.25" style="1" customWidth="1"/>
+    <col min="5" max="5" width="11.25" customWidth="1"/>
+    <col min="10" max="10" width="10.25" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="9" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:16" ht="27" x14ac:dyDescent="0.15">
+    <row r="1" spans="1:17" ht="27" x14ac:dyDescent="0.15">
       <c r="A1" s="5" t="s">
         <v>7</v>
       </c>
@@ -529,43 +533,46 @@
       <c r="C1" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="D1" s="3" t="s">
+      <c r="D1" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="E1" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="E1" s="4" t="s">
+      <c r="F1" s="4" t="s">
         <v>11</v>
       </c>
-      <c r="F1" s="4" t="s">
+      <c r="G1" s="4" t="s">
         <v>12</v>
       </c>
-      <c r="G1" s="4" t="s">
+      <c r="H1" s="4" t="s">
         <v>2</v>
       </c>
-      <c r="H1" s="4" t="s">
+      <c r="I1" s="4" t="s">
         <v>3</v>
       </c>
-      <c r="I1" s="4" t="s">
+      <c r="J1" s="4" t="s">
         <v>4</v>
       </c>
-      <c r="J1" s="4" t="s">
+      <c r="K1" s="4" t="s">
         <v>5</v>
       </c>
-      <c r="K1" s="4" t="s">
+      <c r="L1" s="4" t="s">
         <v>13</v>
       </c>
-      <c r="L1" s="4" t="s">
+      <c r="M1" s="4" t="s">
         <v>14</v>
       </c>
-      <c r="M1" s="4" t="s">
+      <c r="N1" s="4" t="s">
         <v>15</v>
       </c>
-      <c r="N1" s="4" t="s">
+      <c r="O1" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="O1" s="4" t="s">
+      <c r="P1" s="4" t="s">
         <v>8</v>
       </c>
-      <c r="P1" s="4" t="s">
+      <c r="Q1" s="4" t="s">
         <v>9</v>
       </c>
     </row>
